--- a/CHOICES/Denis Bisson.xlsx
+++ b/CHOICES/Denis Bisson.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FakeDrive\Documents\Scripts\Python\pool2024\CHOICES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15DBDA07-0728-4C26-9CC0-4F7BA3648AE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1F4E671-E415-45BA-8E4C-282F991E1D6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{560AF854-FAA8-44CF-BE94-5FF3EB069BA0}"/>
   </bookViews>
@@ -721,7 +721,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -901,6 +901,18 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -1062,8 +1074,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -3141,19 +3155,20 @@
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80">
+      <c r="A80" s="1">
         <v>14</v>
       </c>
-      <c r="B80" t="s">
-        <v>52</v>
-      </c>
-      <c r="C80" t="s">
+      <c r="B80" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C80" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D80" t="s">
+      <c r="D80" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="F80">
+      <c r="E80" s="1"/>
+      <c r="F80" s="1">
         <v>78</v>
       </c>
       <c r="G80" t="str">
@@ -3162,19 +3177,20 @@
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A81">
+      <c r="A81" s="1">
         <v>14</v>
       </c>
-      <c r="B81" t="s">
-        <v>52</v>
-      </c>
-      <c r="C81" t="s">
+      <c r="B81" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C81" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D81" t="s">
+      <c r="D81" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F81">
+      <c r="E81" s="1"/>
+      <c r="F81" s="1">
         <v>79</v>
       </c>
       <c r="G81" t="str">
@@ -3183,19 +3199,20 @@
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82">
+      <c r="A82" s="1">
         <v>14</v>
       </c>
-      <c r="B82" t="s">
-        <v>52</v>
-      </c>
-      <c r="C82" t="s">
+      <c r="B82" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C82" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="D82" t="s">
+      <c r="D82" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F82">
+      <c r="E82" s="1"/>
+      <c r="F82" s="1">
         <v>80</v>
       </c>
       <c r="G82" t="str">
@@ -3204,22 +3221,22 @@
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83">
+      <c r="A83" s="1">
         <v>14</v>
       </c>
-      <c r="B83" t="s">
-        <v>52</v>
-      </c>
-      <c r="C83" t="s">
+      <c r="B83" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C83" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="D83" t="s">
+      <c r="D83" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E83" t="s">
+      <c r="E83" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="F83">
+      <c r="F83" s="1">
         <v>81</v>
       </c>
       <c r="G83">
@@ -3228,19 +3245,20 @@
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84">
+      <c r="A84" s="1">
         <v>14</v>
       </c>
-      <c r="B84" t="s">
-        <v>52</v>
-      </c>
-      <c r="C84" t="s">
+      <c r="B84" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C84" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="D84" t="s">
+      <c r="D84" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F84">
+      <c r="E84" s="1"/>
+      <c r="F84" s="1">
         <v>82</v>
       </c>
       <c r="G84" t="str">
@@ -3249,19 +3267,20 @@
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85">
+      <c r="A85" s="1">
         <v>14</v>
       </c>
-      <c r="B85" t="s">
-        <v>52</v>
-      </c>
-      <c r="C85" t="s">
+      <c r="B85" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C85" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="D85" t="s">
+      <c r="D85" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F85">
+      <c r="E85" s="1"/>
+      <c r="F85" s="1">
         <v>83</v>
       </c>
       <c r="G85" t="str">
@@ -3528,22 +3547,22 @@
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A98">
+      <c r="A98" s="2">
         <v>17</v>
       </c>
-      <c r="B98" t="s">
-        <v>52</v>
-      </c>
-      <c r="C98" t="s">
+      <c r="B98" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C98" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="D98" t="s">
+      <c r="D98" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E98" t="s">
+      <c r="E98" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="F98">
+      <c r="F98" s="2">
         <v>96</v>
       </c>
       <c r="G98">
@@ -3552,19 +3571,20 @@
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A99">
+      <c r="A99" s="2">
         <v>17</v>
       </c>
-      <c r="B99" t="s">
-        <v>52</v>
-      </c>
-      <c r="C99" t="s">
+      <c r="B99" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C99" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="D99" t="s">
+      <c r="D99" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F99">
+      <c r="E99" s="2"/>
+      <c r="F99" s="2">
         <v>97</v>
       </c>
       <c r="G99" t="str">
@@ -3573,19 +3593,20 @@
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100">
+      <c r="A100" s="2">
         <v>17</v>
       </c>
-      <c r="B100" t="s">
-        <v>52</v>
-      </c>
-      <c r="C100" t="s">
+      <c r="B100" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C100" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="D100" t="s">
+      <c r="D100" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F100">
+      <c r="E100" s="2"/>
+      <c r="F100" s="2">
         <v>98</v>
       </c>
       <c r="G100" t="str">
@@ -3594,19 +3615,20 @@
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101">
+      <c r="A101" s="2">
         <v>17</v>
       </c>
-      <c r="B101" t="s">
-        <v>52</v>
-      </c>
-      <c r="C101" t="s">
+      <c r="B101" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C101" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="D101" t="s">
+      <c r="D101" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F101">
+      <c r="E101" s="2"/>
+      <c r="F101" s="2">
         <v>99</v>
       </c>
       <c r="G101" t="str">
@@ -3615,19 +3637,20 @@
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102">
+      <c r="A102" s="2">
         <v>17</v>
       </c>
-      <c r="B102" t="s">
-        <v>52</v>
-      </c>
-      <c r="C102" t="s">
+      <c r="B102" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C102" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="D102" t="s">
+      <c r="D102" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F102">
+      <c r="E102" s="2"/>
+      <c r="F102" s="2">
         <v>100</v>
       </c>
       <c r="G102" t="str">
@@ -3636,19 +3659,20 @@
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103">
+      <c r="A103" s="2">
         <v>17</v>
       </c>
-      <c r="B103" t="s">
-        <v>52</v>
-      </c>
-      <c r="C103" t="s">
+      <c r="B103" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C103" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="D103" t="s">
+      <c r="D103" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F103">
+      <c r="E103" s="2"/>
+      <c r="F103" s="2">
         <v>101</v>
       </c>
       <c r="G103" t="str">
